--- a/AAII_Financials/Quarterly/SCGPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCGPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>SCGPY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
@@ -671,61 +671,76 @@
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +780,20 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +833,20 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +886,20 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +915,12 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +960,20 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +1013,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1066,20 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1119,20 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1145,12 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1190,20 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1243,20 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1272,12 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1317,20 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1370,20 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1423,20 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1476,20 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1529,20 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1582,20 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1635,20 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1688,20 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1741,20 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1794,20 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1847,20 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1900,20 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1953,20 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +2006,20 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +2059,20 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +2112,78 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2199,12 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,49 +2220,65 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>241700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>240600</v>
+      </c>
+      <c r="F41" s="3">
+        <v>268200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>267900</v>
+      </c>
+      <c r="H41" s="3">
         <v>237800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>224300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>229100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>245300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>180000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>179800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>120200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>115200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>125400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>122100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>68900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>63700</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1959,49 +2318,73 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>986600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>981900</v>
+      </c>
+      <c r="F43" s="3">
+        <v>793300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>792300</v>
+      </c>
+      <c r="H43" s="3">
         <v>957300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>902700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>753300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>806500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>852200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>851600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>769600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>737300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>832000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>810000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>804000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>743600</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2009,245 +2392,317 @@
         <v>30000</v>
       </c>
       <c r="E44" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>26900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>30000</v>
+      </c>
+      <c r="I44" s="3">
         <v>28300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>30200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>32300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>31500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>31400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>30700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>29400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>29400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>28600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>27000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>6200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>4300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1259000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1193500</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1192000</v>
+      </c>
+      <c r="H46" s="3">
         <v>1226100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>1156200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>1082400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>1158800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>1065000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>1064300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>997100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>955300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>991100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>964800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>980800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>907000</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>45900</v>
+      </c>
+      <c r="G47" s="3">
+        <v>45800</v>
+      </c>
+      <c r="H47" s="3">
         <v>33800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>31900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>31400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>33600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>48200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>48100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>40900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>39200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>47400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>46100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>28100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>706400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>703000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>725400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>724500</v>
+      </c>
+      <c r="H48" s="3">
         <v>776100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>731900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>715700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>766300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>688100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>687700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>618000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>592100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>596600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>580800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>581100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>537400</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1446600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1439700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1462400</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1460600</v>
+      </c>
+      <c r="H49" s="3">
         <v>1492100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>1407100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>1154900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>1236400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>1334200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>1333300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>1296600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>1242200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>1324800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>1289700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>1327100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>1227300</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2742,20 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2795,73 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>23000</v>
+      </c>
+      <c r="H52" s="3">
         <v>24000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>22600</v>
       </c>
-      <c r="F52" s="3">
-        <v>52000</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
+        <v>33300</v>
+      </c>
+      <c r="K52" s="3">
         <v>55600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>26900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>26900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>66500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>63700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>40800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>39700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>88400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>81800</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2901,73 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3790900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3772900</v>
+      </c>
+      <c r="F54" s="3">
+        <v>3763100</v>
+      </c>
+      <c r="G54" s="3">
+        <v>3758400</v>
+      </c>
+      <c r="H54" s="3">
         <v>3885900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>3664500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>3330500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>3565600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>3482400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>3480100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>3324900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>3185400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>3329100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>3240900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>3313700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>3064500</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2983,12 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +3004,330 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>829200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>825300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>131600</v>
+      </c>
+      <c r="G57" s="3">
+        <v>131500</v>
+      </c>
+      <c r="H57" s="3">
         <v>803300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>757500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>115600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>123700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>738700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>738200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>126500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>121200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>704100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>685500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>130500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>120700</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>229000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>227900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>224900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>224600</v>
+      </c>
+      <c r="H58" s="3">
         <v>290200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>273600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>259300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>277600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>193400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>193200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>243300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>233100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>373500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>363600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>227600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>250500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>249300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>453200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>452600</v>
+      </c>
+      <c r="H59" s="3">
         <v>191300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>180400</v>
       </c>
-      <c r="F59" s="3">
-        <v>384000</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
+        <v>442700</v>
+      </c>
+      <c r="K59" s="3">
         <v>411100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>164300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>164200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>367900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>352400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>146600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>142800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>469800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>434500</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1365800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1359300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1281600</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1279900</v>
+      </c>
+      <c r="H60" s="3">
         <v>1345800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>1269100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>1240700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>1328200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>1168400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>1167600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>1143600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>1095600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>1288700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>1254600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>1234100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>1141300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>972900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>968300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>998900</v>
+      </c>
+      <c r="G61" s="3">
+        <v>997700</v>
+      </c>
+      <c r="H61" s="3">
         <v>1021000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>962800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>750300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>803200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>784400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>783900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>597300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>572200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>584300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>568800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>626500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>127100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>126500</v>
+      </c>
+      <c r="F62" s="3">
+        <v>126800</v>
+      </c>
+      <c r="G62" s="3">
+        <v>126600</v>
+      </c>
+      <c r="H62" s="3">
         <v>126900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>119600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>129600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>138700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>113700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>113700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>110600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>105900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>96100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>93500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>96400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3367,20 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3420,20 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3473,73 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2637000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2624400</v>
+      </c>
+      <c r="F66" s="3">
+        <v>2587300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2584100</v>
+      </c>
+      <c r="H66" s="3">
         <v>2692100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>2538800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>2275700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>2436400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>2225300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>2223900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>2008200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>1923900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>2079300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>2024200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>2073000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>1917100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3555,12 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3600,20 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3653,20 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3706,20 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3759,73 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>853300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>849200</v>
+      </c>
+      <c r="F72" s="3">
+        <v>776600</v>
+      </c>
+      <c r="G72" s="3">
+        <v>775600</v>
+      </c>
+      <c r="H72" s="3">
         <v>800800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>755200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>656400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>702700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>855600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>855000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>839500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>804300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>1012300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>985500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>808000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>747200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3865,20 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3918,20 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3971,73 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1153900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1148400</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1175800</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1174300</v>
+      </c>
+      <c r="H76" s="3">
         <v>1193700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>1125700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>1054700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>1129200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>1257100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>1256300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>1317100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>1261800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>1250200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>1217100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>1238900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>1145700</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +4077,78 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +4188,20 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +4217,65 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>56800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>52500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>56200</v>
+      </c>
+      <c r="H83" s="3">
         <v>47300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>47300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>45000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>43100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>45800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>44600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>43900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>40600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>40800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>44200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>41100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +4315,20 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +4368,20 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4421,20 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4474,20 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4527,73 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>120700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>120100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>169700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>169400</v>
+      </c>
+      <c r="H89" s="3">
         <v>133300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>125700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>144200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>154400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>119400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>119400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>117400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>112500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>132700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>129200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>86200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>79700</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +4609,65 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-6800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-8300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-8100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-6700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4707,20 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4760,73 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-169000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-159400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="J94" s="3">
         <v>6100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>6500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-10800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-10800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-6600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-6400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-14300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4842,65 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F96" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G96" s="3">
+        <v>9900</v>
+      </c>
+      <c r="H96" s="3">
         <v>19600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>18500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>8700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>9300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="L96" s="3">
         <v>15500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="M96" s="3">
         <v>15500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="N96" s="3">
         <v>8000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>7600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="P96" s="3">
         <v>13500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="Q96" s="3">
         <v>13100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="R96" s="3">
         <v>6600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4940,20 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4993,20 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +5046,175 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-134900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-134300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-150700</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-150500</v>
+      </c>
+      <c r="H100" s="3">
         <v>32900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>31000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-124900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-133800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-77500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-77500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-123200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-118000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-98200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-95600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-145800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-134800</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>100</v>
+      </c>
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>17300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>17300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>-6100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>25400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>27200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>30300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>30300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>26400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>25700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-73300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-67800</v>
       </c>
     </row>
